--- a/output/laminas_comunales/comunal_s_isapre_a_2023_maule.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2023_maule.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>26617</v>
+        <v>11.14176161812352</v>
       </c>
     </row>
     <row r="3">
@@ -399,22 +399,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>16724</v>
+        <v>9.840251831367127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="C4">
-        <v>7339</v>
+        <v>6.847673046919594</v>
       </c>
     </row>
     <row r="5">
@@ -429,352 +429,352 @@
         </is>
       </c>
       <c r="C5">
-        <v>3630</v>
+        <v>6.721475391623153</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="C6">
-        <v>3599</v>
+        <v>6.705957602339181</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Pencahue</t>
         </is>
       </c>
       <c r="C7">
-        <v>2480</v>
+        <v>6.423371117869321</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="C8">
-        <v>2007</v>
+        <v>6.355158632259338</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Molina</t>
+          <t>Licantén</t>
         </is>
       </c>
       <c r="C9">
-        <v>2000</v>
+        <v>5.773006938080901</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Vichuquén</t>
         </is>
       </c>
       <c r="C10">
-        <v>1997</v>
+        <v>5.030391951372878</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>San Clemente</t>
+          <t>San Rafael</t>
         </is>
       </c>
       <c r="C11">
-        <v>1717</v>
+        <v>5.007620291748313</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Romeral</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="C12">
-        <v>1288</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Teno</t>
+          <t>Pelarco</t>
         </is>
       </c>
       <c r="C13">
-        <v>1209</v>
+        <v>4.562495014756322</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
+          <t>Pelluhue</t>
         </is>
       </c>
       <c r="C14">
-        <v>924</v>
+        <v>4.551258664720905</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Longaví</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="C15">
-        <v>858</v>
+        <v>4.389131673950218</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Colbún</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="C16">
-        <v>814</v>
+        <v>4.189481192439214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pencahue</t>
+          <t>Rauco</t>
         </is>
       </c>
       <c r="C17">
-        <v>697</v>
+        <v>4.018329221008107</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>San Rafael</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="C18">
-        <v>690</v>
+        <v>3.895901511609786</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
+          <t>Hualañé</t>
         </is>
       </c>
       <c r="C19">
-        <v>594</v>
+        <v>3.859882128330705</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="C20">
-        <v>574</v>
+        <v>3.825772016774685</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pelarco</t>
+          <t>Teno</t>
         </is>
       </c>
       <c r="C21">
-        <v>572</v>
+        <v>3.789968652037618</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Retiro</t>
+          <t>Curepto</t>
         </is>
       </c>
       <c r="C22">
-        <v>571</v>
+        <v>3.463082236535051</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Río Claro</t>
+          <t>San Clemente</t>
         </is>
       </c>
       <c r="C23">
-        <v>518</v>
+        <v>3.415012530331357</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pelluhue</t>
+          <t>Colbún</t>
         </is>
       </c>
       <c r="C24">
-        <v>499</v>
+        <v>3.250279508065804</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hualañé</t>
+          <t>Villa Alegre</t>
         </is>
       </c>
       <c r="C25">
-        <v>465</v>
+        <v>3.235999128350403</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rauco</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="C26">
-        <v>456</v>
+        <v>3.108124324972999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Yerbas Buenas</t>
         </is>
       </c>
       <c r="C27">
-        <v>441</v>
+        <v>2.693823915900131</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Curepto</t>
+          <t>Retiro</t>
         </is>
       </c>
       <c r="C28">
-        <v>371</v>
+        <v>2.507575424882526</v>
       </c>
     </row>
     <row r="29">
@@ -789,22 +789,22 @@
         </is>
       </c>
       <c r="C29">
-        <v>242</v>
+        <v>2.501291989664083</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
+          <t>Longaví</t>
         </is>
       </c>
       <c r="C30">
-        <v>240</v>
+        <v>2.260512171988618</v>
       </c>
     </row>
     <row r="31">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>66</v>
+        <v>1.699279093717817</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +875,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
